--- a/tasks/finalpool/yf-financial-statements-overview/groundtruth_workspace/YF_Financial_Statements.xlsx
+++ b/tasks/finalpool/yf-financial-statements-overview/groundtruth_workspace/YF_Financial_Statements.xlsx
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
